--- a/artfynd/A 9539-2026 artfynd.xlsx
+++ b/artfynd/A 9539-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104091673</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599870.9619994457</v>
+        <v>599871</v>
       </c>
       <c r="R2" t="n">
-        <v>6548557.504864244</v>
+        <v>6548557</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104091790</v>
+        <v>104098573</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,14 +817,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Töversta 600m N, Srm</t>
+          <t>Haganäs 200m SO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599774.3238572369</v>
+        <v>599683</v>
       </c>
       <c r="R3" t="n">
-        <v>6548587.396105452</v>
+        <v>6548767</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +854,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104098573</v>
+        <v>104091790</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,14 +924,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Haganäs 200m SO, Srm</t>
+          <t>Töversta 600m N, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>599683.5776817129</v>
+        <v>599775</v>
       </c>
       <c r="R4" t="n">
-        <v>6548767.143977595</v>
+        <v>6548587</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,19 +961,9 @@
           <t>2022-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9539-2026 artfynd.xlsx
+++ b/artfynd/A 9539-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104091673</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104098573</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104091790</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>